--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_319_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_319_R32.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.58</v>
+        <v>5.7638</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8304</v>
+        <v>3.4765</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7496</v>
+        <v>2.2873</v>
       </c>
       <c r="G2" t="n">
         <v>3.4114</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.919</v>
+        <v>-0.7352</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5421</v>
+        <v>-0.896</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3769</v>
+        <v>0.1608</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4171</v>
+        <v>3.4926</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7591</v>
+        <v>1.6411</v>
       </c>
       <c r="F3" t="n">
-        <v>2.658</v>
+        <v>1.8514</v>
       </c>
       <c r="G3" t="n">
         <v>2.3948</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4708</v>
+        <v>0.5463</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2794</v>
+        <v>0.1614</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1914</v>
+        <v>0.3848</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2713</v>
+        <v>3.4894</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2143</v>
+        <v>1.0964</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0569</v>
+        <v>2.393</v>
       </c>
       <c r="G4" t="n">
         <v>1.3355</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.224</v>
+        <v>-0.0059</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2794</v>
+        <v>0.1614</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5034</v>
+        <v>-0.1674</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2238</v>
+        <v>1.1902</v>
       </c>
       <c r="E6" t="n">
         <v>1.1472</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0766</v>
+        <v>0.043</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9134</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6515</v>
+        <v>-0.6851</v>
       </c>
       <c r="T6" t="n">
         <v>-0.8962</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2447</v>
+        <v>0.2111</v>
       </c>
       <c r="V6" t="n">
         <v>1.8608</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0261</v>
+        <v>0.3496</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3905</v>
+        <v>-1.7392</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4166</v>
+        <v>2.0888</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9146</v>
+        <v>1.6903</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8643</v>
+        <v>0.6196</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0502</v>
+        <v>1.0707</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0755</v>
+        <v>0.7648</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0755</v>
+        <v>0.4236</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.3412</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1609</v>
+        <v>0.9255</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2112</v>
+        <v>0.196</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0502</v>
+        <v>0.7296</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3066</v>
+        <v>0.051</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5623</v>
+        <v>-0.1845</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2557</v>
+        <v>0.2355</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1222</v>
+        <v>-0.3799</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.211</v>
+        <v>0.0367</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0888</v>
+        <v>-0.4166</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6903</v>
+        <v>0.9146</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6196</v>
+        <v>0.8643</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0707</v>
+        <v>0.0502</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7648</v>
+        <v>1.0755</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4236</v>
+        <v>1.0755</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3412</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9255</v>
+        <v>-0.1609</v>
       </c>
       <c r="N8" t="n">
-        <v>0.196</v>
+        <v>-0.2112</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7296</v>
+        <v>0.0502</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4208</v>
+        <v>-0.0472</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6563</v>
+        <v>0.2084</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2355</v>
+        <v>-0.2557</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8396</v>
+        <v>-0.4021</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4774</v>
+        <v>-1.2415</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6378</v>
+        <v>0.8394</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3529</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7187</v>
+        <v>-0.2812</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.229</v>
+        <v>-2.164</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4652</v>
+        <v>-4.2549</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2362</v>
+        <v>2.0909</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3397</v>
+        <v>3.1001</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8149</v>
+        <v>2.8426</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4752</v>
+        <v>0.2575</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3062</v>
+        <v>3.7294</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4166</v>
+        <v>3.4653</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1104</v>
+        <v>0.264</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0335</v>
+        <v>-0.6293</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3983</v>
+        <v>-0.6227</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3648</v>
+        <v>-0.0065</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6237</v>
+        <v>-4.639</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.5515</v>
+        <v>-7.1905</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3378</v>
+        <v>-0.6251</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8215</v>
+        <v>-0.7938</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4837</v>
+        <v>0.1687</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3999</v>
+        <v>-2.4643</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4908</v>
+        <v>-2.4652</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0909</v>
+        <v>0.0009</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1001</v>
+        <v>-1.3397</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8426</v>
+        <v>-1.8149</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2575</v>
+        <v>0.4752</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7294</v>
+        <v>-0.3062</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4653</v>
+        <v>-0.4166</v>
       </c>
       <c r="L13" t="n">
-        <v>0.264</v>
+        <v>0.1104</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6293</v>
+        <v>-1.0335</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6227</v>
+        <v>-1.3983</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0065</v>
+        <v>0.3648</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.1905</v>
+        <v>-2.5515</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.861</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0297</v>
+        <v>-0.8215</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1687</v>
+        <v>0.2484</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.039500000000002</v>
+        <v>8.039400000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.557999999999998</v>
+        <v>-1.557999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>9.597400000000002</v>
+        <v>9.597300000000001</v>
       </c>
       <c r="G14" t="n">
         <v>12.49</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6103</v>
+        <v>4.610300000000001</v>
       </c>
       <c r="I14" t="n">
         <v>7.879600000000001</v>
@@ -1546,13 +1546,13 @@
         <v>13.9173</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.5977</v>
+        <v>-3.597799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.243600000000001</v>
+        <v>-4.2438</v>
       </c>
       <c r="U14" t="n">
-        <v>0.646</v>
+        <v>0.6457999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.4665</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4543</v>
+        <v>2.7016</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7348</v>
+        <v>1.7912</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7195</v>
+        <v>0.9104</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1566</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8429</v>
+        <v>1.0901</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5454</v>
+        <v>0.6018</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2974</v>
+        <v>0.4883</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9555</v>
+        <v>1.6137</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5825</v>
+        <v>2.285</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.627</v>
+        <v>-0.6714</v>
       </c>
       <c r="G16" t="n">
         <v>-1.542</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2835</v>
+        <v>0.9416</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3961</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8874</v>
+        <v>0.843</v>
       </c>
       <c r="V16" t="n">
         <v>1.7501</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9351</v>
+        <v>1.3124</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5713</v>
+        <v>1.2174</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3639</v>
+        <v>0.095</v>
       </c>
       <c r="G17" t="n">
         <v>0.5012</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2046</v>
+        <v>0.5819</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.6721</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9304</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4403</v>
+        <v>0.8973</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0473</v>
+        <v>0.6475</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4876</v>
+        <v>0.2498</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8718</v>
+        <v>0.2043</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8919</v>
+        <v>-1.144</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0201</v>
+        <v>1.3483</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4754</v>
+        <v>0.8479</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7023</v>
+        <v>-0.4502</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1778</v>
+        <v>1.2981</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3473</v>
+        <v>-0.6435</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1896</v>
+        <v>-0.6938</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1577</v>
+        <v>0.0502</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1344</v>
+        <v>-0.2348</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5228</v>
+        <v>-0.2003</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6572</v>
+        <v>-0.0345</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2575</v>
+        <v>0.4238</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1757</v>
+        <v>0.0706</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0818</v>
+        <v>0.3532</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2043</v>
+        <v>-0.8718</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.144</v>
+        <v>-0.8919</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3483</v>
+        <v>0.0201</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8479</v>
+        <v>0.4754</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4502</v>
+        <v>-0.7023</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2981</v>
+        <v>1.1778</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6435</v>
+        <v>-1.3473</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6938</v>
+        <v>-0.1896</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0502</v>
+        <v>-1.1577</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8746</v>
+        <v>0.118</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>-0.4048</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2025</v>
+        <v>0.5228</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3642</v>
+        <v>-0.1333</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6618</v>
+        <v>-1.5438</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2976</v>
+        <v>1.4105</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0826</v>
@@ -2014,13 +2014,13 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8602</v>
+        <v>1.091</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2434</v>
+        <v>-0.1254</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1035</v>
+        <v>1.2164</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1418</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9867</v>
+        <v>-1.5707</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2124</v>
+        <v>-2.9765</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2257</v>
+        <v>1.4058</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8249</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1423</v>
+        <v>0.5583</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3181</v>
+        <v>-0.0822</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4604</v>
+        <v>0.6405</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1013</v>
+        <v>-2.2535</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.508</v>
+        <v>-2.9182</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4066</v>
+        <v>0.6647</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4655</v>
@@ -2170,13 +2170,13 @@
         <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6875</v>
+        <v>0.1603</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3443</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.2836</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4342</v>
+        <v>-2.8</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1052</v>
+        <v>-2.9872</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.329</v>
+        <v>0.1872</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2674</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.007</v>
+        <v>0.6271</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0553</v>
+        <v>0.1733</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0624</v>
+        <v>0.4538</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.195600000000001</v>
+        <v>-6.6578</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1269</v>
+        <v>-5.1833</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0687</v>
+        <v>-1.4745</v>
       </c>
       <c r="G24" t="n">
         <v>-3.985</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3008</v>
+        <v>0.237</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8057</v>
+        <v>0.1379</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4951</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7501</v>
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.039300000000001</v>
+        <v>-6.4665</v>
       </c>
       <c r="E25" t="n">
         <v>-9.597300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>1.558</v>
+        <v>3.1307</v>
       </c>
       <c r="G25" t="n">
         <v>-12.4903</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.610200000000001</v>
+        <v>-4.6102</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.879700000000001</v>
+        <v>-7.8797</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6458000000000004</v>
+        <v>0.6457999999999995</v>
       </c>
       <c r="K25" t="n">
         <v>3.491</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.8452</v>
+        <v>-2.845199999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-13.136</v>
@@ -2404,13 +2404,13 @@
         <v>16.2367</v>
       </c>
       <c r="S25" t="n">
-        <v>3.598000000000002</v>
+        <v>5.170500000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6459999999999999</v>
+        <v>-0.6459</v>
       </c>
       <c r="U25" t="n">
-        <v>4.2437</v>
+        <v>5.8163</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4665</v>
